--- a/output/pdf_financials_xlsx/WSR.xlsx
+++ b/output/pdf_financials_xlsx/WSR.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.565723</v>
+        <v>-0.565723</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.088118</v>
+        <v>-1.088118</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.573933</v>
+        <v>-1.573933</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.565723</v>
+        <v>-0.565723</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.088118</v>
+        <v>-1.088118</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.573933</v>
+        <v>-1.573933</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.565723</v>
+        <v>-0.565723</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.088118</v>
+        <v>-1.088118</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.573933</v>
+        <v>-1.573933</v>
       </c>
     </row>
     <row r="24">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-2.09527</v>
+        <v>2.09527</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-3.510058</v>
+        <v>3.510058</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-11.242379</v>
+        <v>11.242379</v>
       </c>
     </row>
     <row r="27">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.565723</v>
+        <v>-0.565723</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.088118</v>
+        <v>-1.088118</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.573933</v>
+        <v>-1.573933</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.565723</v>
+        <v>-0.565723</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.088118</v>
+        <v>-1.088118</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.573933</v>
+        <v>-1.573933</v>
       </c>
     </row>
     <row r="30">
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.059711</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.126651</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.44123</v>
       </c>
     </row>
     <row r="93">
@@ -3088,7 +3088,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.059711</v>
       </c>
@@ -4799,13 +4803,13 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.565723</v>
+        <v>-0.565723</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>1.088118</v>
+        <v>-1.088118</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>1.573933</v>
+        <v>-1.573933</v>
       </c>
     </row>
     <row r="73">

--- a/output/pdf_financials_xlsx/WSR.xlsx
+++ b/output/pdf_financials_xlsx/WSR.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001803</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.026391</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.046211</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001803</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.026391</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.046211</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.001803</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.026391</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.07129000000000001</v>
+        <v>0.025079</v>
       </c>
     </row>
     <row r="49">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
